--- a/ai-test-framework/datasets/excel/D_小韩面无人值守门禁.xlsx
+++ b/ai-test-framework/datasets/excel/D_小韩面无人值守门禁.xlsx
@@ -12,7 +12,7 @@
     <sheet name="汇总" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'用例明细'!$A$1:$K$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'用例明细'!$A$1:$K$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -572,17 +572,23 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_door_lock_status",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517"
+ }
 }</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>查询设备终端列表</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517"}</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Skill 正确触发执行</t>
@@ -595,7 +601,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>contains: 门锁设备状态  fields: 设备状态 | 锁定状态 | 提示 在线 | 离线</t>
+          <t>contains: Test  fields: 含 终端</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,7 +623,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -628,19 +634,25 @@
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_door_lock_status",
- "tool_params": {
-  "unknown_param_malformed": "x"
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ]
  }
 }</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>查询设备终端列表</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517"}</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>非法输入按契约拒绝</t>
@@ -653,7 +665,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>contains: 门锁设备状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -675,7 +687,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -686,9 +698,11 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_door_lock_status",
- "tool_params": {
-  "_out_of_range_": "9999999999999999"
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ]
  }
 }</t>
         </is>
@@ -711,7 +725,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>contains: 门锁设备状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -733,7 +747,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -744,7 +758,7 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_door_lock_status",
+ "tool_name": "query_device_terminals",
  "tool_params": {
   "_invalid": ""
  }
@@ -769,7 +783,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>contains: 门锁设备状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -791,7 +805,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -802,17 +816,23 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_door_lock_status",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517"
+ }
 }</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>查询设备终端列表</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517"}</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>单次调用延迟可接受</t>
@@ -825,7 +845,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>contains: 门锁设备状态  fields: 设备状态 | 锁定状态 | 提示 在线 | 离线</t>
+          <t>contains: Test  fields: 含 终端</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -847,7 +867,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -858,17 +878,26 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_unattended_status",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ]
+ }
 }</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>查询设备终端详情</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"]}</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Skill 正确触发执行</t>
@@ -881,7 +910,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>contains: 当前值守模式状态  fields: 值守模式 | 批次编号 | 提示 开启时间</t>
+          <t>fields: 含端口 ID | 索引 | 设备名称</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -903,7 +932,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -914,19 +943,28 @@
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_unattended_status",
- "tool_params": {
-  "unknown_param_malformed": "x"
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ],
+  "terminalIds": [
+   "26456010686725"
+  ]
  }
 }</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>查询设备终端详情</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"]}</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>非法输入按契约拒绝</t>
@@ -939,7 +977,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>contains: 当前值守模式状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -961,7 +999,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -972,9 +1010,14 @@
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_unattended_status",
- "tool_params": {
-  "_out_of_range_": "9999999999999999"
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ],
+  "terminalIds": [
+   "26456010686725"
+  ]
  }
 }</t>
         </is>
@@ -997,7 +1040,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>contains: 当前值守模式状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1019,7 +1062,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1030,7 +1073,7 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_unattended_status",
+ "tool_name": "query_device_terminals",
  "tool_params": {
   "_invalid": ""
  }
@@ -1055,7 +1098,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>contains: 当前值守模式状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1077,7 +1120,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1088,17 +1131,26 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_unattended_status",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ]
+ }
 }</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>查询设备终端详情</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"]}</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>单次调用延迟可接受</t>
@@ -1111,7 +1163,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>contains: 当前值守模式状态  fields: 值守模式 | 批次编号 | 提示 开启时间</t>
+          <t>fields: 含端口 ID | 索引 | 设备名称</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1133,7 +1185,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>开启无人值守模式</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1144,17 +1196,24 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {}
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true
+ }
 }</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>开启无人值守模式</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Skill 正确触发执行</t>
@@ -1167,7 +1226,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>contains: 开启结果  fields: 批次编号 | 已开启 | 提示 门锁已上锁</t>
+          <t>contains: isEnable</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1189,7 +1248,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>开启无人值守模式</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1200,19 +1259,26 @@
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "unknown_param_malformed": "x"
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ],
+  "isEnabled": true
  }
 }</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+          <t>开启无人值守模式</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>非法输入按契约拒绝</t>
@@ -1225,7 +1291,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>contains: 开启结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1247,7 +1313,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>开启无人值守模式</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1258,9 +1324,12 @@
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "_out_of_range_": "9999999999999999"
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ],
+  "isEnabled": true
  }
 }</t>
         </is>
@@ -1283,7 +1352,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>contains: 开启结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1305,7 +1374,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>开启无人值守模式</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1316,7 +1385,7 @@
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
+ "tool_name": "set_device_terminal_unattended_mode",
  "tool_params": {
   "_invalid": ""
  }
@@ -1341,7 +1410,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>contains: 开启结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1363,7 +1432,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>开启无人值守模式</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1374,17 +1443,24 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {}
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true
+ }
 }</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>开启无人值守模式</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>单次调用延迟可接受</t>
@@ -1397,7 +1473,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>contains: 开启结果  fields: 批次编号 | 已开启 | 提示 门锁已上锁</t>
+          <t>contains: isEnable</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1419,7 +1495,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1430,17 +1506,24 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>{
- "tool_name": "disable_unattended_mode",
- "tool_params": {}
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true
+ }
 }</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Skill 正确触发执行</t>
@@ -1453,7 +1536,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>contains: 关闭结果  fields: 已关闭 | 批次封存</t>
+          <t>contains: isEnable</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1475,7 +1558,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1486,19 +1569,26 @@
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "disable_unattended_mode",
- "tool_params": {
-  "unknown_param_malformed": "x"
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ],
+  "isEnabled": true
  }
 }</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>非法输入按契约拒绝</t>
@@ -1511,7 +1601,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>contains: 关闭结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1533,7 +1623,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1544,9 +1634,12 @@
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "disable_unattended_mode",
- "tool_params": {
-  "_out_of_range_": "9999999999999999"
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ],
+  "isEnabled": true
  }
 }</t>
         </is>
@@ -1569,7 +1662,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>contains: 关闭结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1591,7 +1684,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1602,7 +1695,7 @@
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "disable_unattended_mode",
+ "tool_name": "set_device_terminal_unattended_mode",
  "tool_params": {
   "_invalid": ""
  }
@@ -1627,7 +1720,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>contains: 关闭结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1649,7 +1742,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1660,17 +1753,24 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>{
- "tool_name": "disable_unattended_mode",
- "tool_params": {}
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true
+ }
 }</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>单次调用延迟可接受</t>
@@ -1683,7 +1783,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>contains: 关闭结果  fields: 已关闭 | 批次封存</t>
+          <t>contains: isEnable</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1705,7 +1805,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1716,23 +1816,23 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1747,7 +1847,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fields: 进场人次 | 离场人次 | 事件类型 | 提示 日期范围</t>
+          <t>contains: Test  fields: 含前门端口 | 操作来源</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1769,7 +1869,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1780,23 +1880,25 @@
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "9999-99-99",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1811,7 +1913,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1833,7 +1935,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1844,11 +1946,13 @@
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "9999-99-99",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
@@ -1871,7 +1975,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1893,7 +1997,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1904,7 +2008,7 @@
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
+ "tool_name": "query_device_terminal_port_state_records",
  "tool_params": {
   "_invalid": ""
  }
@@ -1929,7 +2033,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1951,7 +2055,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1962,23 +2066,23 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1993,7 +2097,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fields: 进场人次 | 离场人次 | 事件类型 | 提示 日期范围</t>
+          <t>contains: Test  fields: 含前门端口 | 操作来源</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2015,7 +2119,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2026,17 +2130,27 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_remaining_visitors",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "startTime": "",
+  "endTime": "",
+  "page": 1,
+  "size": 10
+ }
 }</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>按时间范围查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "startTime": "", "endTime": "", "page": 1, "size": 10}</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Skill 正确触发执行</t>
@@ -2049,7 +2163,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>contains: 未离场人员清单  fields: 手机号 | 进场时间 | 逗留时长</t>
+          <t>contains: 端口操作记录</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2071,7 +2185,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2082,19 +2196,29 @@
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_remaining_visitors",
- "tool_params": {
-  "unknown_param_malformed": "x"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ],
+  "startTime": "",
+  "endTime": "",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>按时间范围查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "startTime": "", "endTime": "", "page": 1, "size": 10}</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>非法输入按契约拒绝</t>
@@ -2107,7 +2231,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>contains: 未离场人员清单 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2129,7 +2253,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2140,9 +2264,15 @@
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_remaining_visitors",
- "tool_params": {
-  "_out_of_range_": "9999999999999999"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ],
+  "startTime": "",
+  "endTime": "",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
@@ -2165,7 +2295,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>contains: 未离场人员清单 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2187,7 +2317,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2198,7 +2328,7 @@
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_remaining_visitors",
+ "tool_name": "query_device_terminal_port_state_records",
  "tool_params": {
   "_invalid": ""
  }
@@ -2223,7 +2353,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>contains: 未离场人员清单 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2245,7 +2375,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2256,17 +2386,27 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_remaining_visitors",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "startTime": "",
+  "endTime": "",
+  "page": 1,
+  "size": 10
+ }
 }</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>按时间范围查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "startTime": "", "endTime": "", "page": 1, "size": 10}</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>单次调用延迟可接受</t>
@@ -2279,7 +2419,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>contains: 未离场人员清单  fields: 手机号 | 进场时间 | 逗留时长</t>
+          <t>contains: 端口操作记录</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2301,7 +2441,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2312,23 +2452,24 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "operationSources": "",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2343,7 +2484,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>contains: 无进出记录  fields: 无进出记录</t>
+          <t>contains: 记录</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2365,7 +2506,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2376,23 +2517,26 @@
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "9999-99-99",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ],
+  "operationSources": "",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2407,7 +2551,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>contains: 无进出记录 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2429,7 +2573,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2440,11 +2584,14 @@
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "9999-99-99",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ],
+  "operationSources": "",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
@@ -2467,7 +2614,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>contains: 无进出记录 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2489,7 +2636,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2500,7 +2647,7 @@
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
+ "tool_name": "query_device_terminal_port_state_records",
  "tool_params": {
   "_invalid": ""
  }
@@ -2525,7 +2672,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>contains: 无进出记录 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2547,7 +2694,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2558,23 +2705,24 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "operationSources": "",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2589,7 +2737,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>contains: 无进出记录  fields: 无进出记录</t>
+          <t>contains: 记录</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2611,7 +2759,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2622,21 +2770,29 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "storeId": "XHM-BATCH-002"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>{"storeId": "XHM-BATCH-002"}</t>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "portIds": ["26456101370181"], "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2651,7 +2807,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fields: 无权限 | 错误</t>
+          <t>contains: 记录</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2673,7 +2829,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2684,23 +2840,31 @@
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "storeId": [
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
    "0"
-  ]
+  ],
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>{"storeId": "XHM-BATCH-002"}</t>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "portIds": ["26456101370181"], "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2715,7 +2879,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2737,7 +2901,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2748,11 +2912,19 @@
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "storeId": [
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
    "9999999999999999"
-  ]
+  ],
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
@@ -2775,7 +2947,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2797,7 +2969,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2808,7 +2980,7 @@
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
+ "tool_name": "query_device_terminal_port_state_records",
  "tool_params": {
   "_invalid": ""
  }
@@ -2833,7 +3005,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2855,7 +3027,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2866,21 +3038,29 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "storeId": "XHM-BATCH-002"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{"storeId": "XHM-BATCH-002"}</t>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "portIds": ["26456101370181"], "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2895,7 +3075,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fields: 无权限 | 错误</t>
+          <t>contains: 记录</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2917,7 +3097,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2928,17 +3108,24 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>{
- "tool_name": "unlock_door",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true
+ }
 }</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Skill 正确触发执行</t>
@@ -2949,11 +3136,7 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fields: 不支持 | 拒绝</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>正常</t>
@@ -2973,7 +3156,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2984,19 +3167,26 @@
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "unlock_door",
- "tool_params": {
-  "unknown_param_malformed": "x"
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ],
+  "isEnabled": true
  }
 }</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>非法输入按契约拒绝</t>
@@ -3009,7 +3199,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3031,7 +3221,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3042,9 +3232,12 @@
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "unlock_door",
- "tool_params": {
-  "_out_of_range_": "9999999999999999"
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ],
+  "isEnabled": true
  }
 }</t>
         </is>
@@ -3067,7 +3260,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3089,7 +3282,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3100,7 +3293,7 @@
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "unlock_door",
+ "tool_name": "query_device_terminals",
  "tool_params": {
   "_invalid": ""
  }
@@ -3125,7 +3318,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3147,7 +3340,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3158,17 +3351,24 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>{
- "tool_name": "unlock_door",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true
+ }
 }</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>单次调用延迟可接受</t>
@@ -3179,11 +3379,7 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fields: 不支持 | 拒绝</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>正常</t>
@@ -3203,7 +3399,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3214,17 +3410,25 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 1,
+  "size": 10
+ }
 }</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10}</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Skill 正确触发执行</t>
@@ -3235,11 +3439,7 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fields: 设备离线 | 错误</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>正常</t>
@@ -3259,7 +3459,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3270,19 +3470,27 @@
       <c r="E48" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "unknown_param_malformed": "x"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
+   "0"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10}</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>非法输入按契约拒绝</t>
@@ -3295,7 +3503,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3317,7 +3525,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3328,9 +3536,13 @@
       <c r="E49" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "_out_of_range_": "9999999999999999"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": [
+   "9999999999999999"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
@@ -3353,7 +3565,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3375,7 +3587,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3386,7 +3598,7 @@
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
+ "tool_name": "query_device_terminal_port_state_records",
  "tool_params": {
   "_invalid": ""
  }
@@ -3411,7 +3623,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3433,7 +3645,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3444,17 +3656,25 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 1,
+  "size": 10
+ }
 }</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10}</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>单次调用延迟可接受</t>
@@ -3465,11 +3685,7 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fields: 设备离线 | 错误</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>正常</t>
@@ -3489,31 +3705,33 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>未确认开启</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>与其他Skill组合</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517"
+ }
 }</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>未确认开启</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Skill 正确触发执行</t>
+          <t>查询设备终端列表 与 查询设备终端详情 组合调用无冲突</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3523,608 +3741,655 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>fields: 确认 | 拒绝</t>
+          <t>contains: Test  fields: 含 终端</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>组合</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>D-L1-052</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>未确认开启</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-052</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>输入输出契约</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "unknown_param_malformed": "x"
- }
-}</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>未确认开启</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>非法输入按契约拒绝</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>契约</t>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "isEnabled": true
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>{"isEnabled": true}</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>缺失参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>参数缺失</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>D-L1-053</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>未确认开启</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-053</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>按终端/端口筛选端口记录</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>输入输出契约</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": 1,
+  "size": 10,
+  "unknown_param": "x"
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>按终端/端口筛选端口记录</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "portIds": ["26456101370181"], "page": 1, "size": 10, "unknown_param": "x"}</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>未知参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>参数注入</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-054</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>按时间范围查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>能力边界</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "_out_of_range_": "9999999999999999"
- }
-}</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>越界</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>越界操作被拒绝或提示</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>边界</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>D-L1-054</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>未确认开启</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "startTime": "",
+  "endTime": "",
+  "page": -1,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>按时间范围查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "startTime": "", "endTime": "", "page": -1, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-055</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>能力边界</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": 9999999999999999
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": 9999999999999999}</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>错误处理</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "_invalid": ""
- }
-}</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>容错</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>失败被友好处理，不崩溃</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>容错</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>D-L1-055</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>未确认开启</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>性能</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "enable_unattended_mode",
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": "abc"
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": "abc"}</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>参数类型错误被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>类型错配</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-057</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>错误处理</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": "abc",
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": "abc", "size": 10}</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>参数类型错误被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>类型错配</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>按终端/端口筛选端口记录</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>能力边界</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": -1,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>按终端/端口筛选端口记录</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "portIds": ["26456101370181"], "page": -1, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-059</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>开启无人值守模式</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>输入输出契约</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true,
+  "unknown_param": "x"
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>开启无人值守模式</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true, "unknown_param": "x"}</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>未知参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>参数注入</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>能力边界</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 0,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 0, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-061</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>查询设备终端列表</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>输入输出契约</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminals",
  "tool_params": {}
 }</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>未确认开启</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>单次调用延迟可接受</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fields: 确认 | 拒绝</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>D-L1-056</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>指令注入日志查询</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>触发条件正确性</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
- }
-}</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>指令注入日志查询</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Skill 正确触发执行</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>contains: 参数非法  fields: 参数非法 | 错误</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>D-L1-057</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>指令注入日志查询</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>输入输出契约</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "9999-99-99",
-  "date_to": "今日",
-  "event_type": ""
- }
-}</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>指令注入日志查询</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>非法输入按契约拒绝</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>contains: 参数非法 | 错误 | 拒绝  any_of=true</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>契约</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>D-L1-058</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>指令注入日志查询</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>能力边界</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "9999-99-99",
-  "date_to": "今日",
-  "event_type": ""
- }
-}</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>越界</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>越界操作被拒绝或提示</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>contains: 参数非法 | 错误 | 拒绝  any_of=true</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>边界</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>D-L1-059</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>指令注入日志查询</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>错误处理</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "_invalid": ""
- }
-}</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>容错</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>失败被友好处理，不崩溃</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>contains: 参数非法 | 错误 | 拒绝  any_of=true</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>容错</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>D-L1-060</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>指令注入日志查询</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>性能</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
- }
-}</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>指令注入日志查询</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>单次调用延迟可接受</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>contains: 参数非法  fields: 参数非法 | 错误</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>D-L1-061</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>查询门锁状态</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>与其他Skill组合</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "get_door_lock_status",
- "tool_params": {}
-}</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>查询门锁状态</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>查询门锁状态 与 查询值守状态 组合调用无冲突</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>contains: 门锁设备状态  fields: 设备状态 | 锁定状态 | 提示 在线 | 离线</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>组合</t>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>查询设备终端列表</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>缺失参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>参数缺失</t>
         </is>
       </c>
     </row>
@@ -4141,39 +4406,41 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>输入输出契约</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs_typo",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "operationSources": "",
+  "page": 1,
+  "size": 10,
+  "unknown_param": "x"
  }
 }</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": 1, "size": 10, "unknown_param": "x"}</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>未知参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -4183,12 +4450,12 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>参数注入</t>
         </is>
       </c>
     </row>
@@ -4205,37 +4472,38 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>触发条件正确性</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "unknown_param": "x"
+ "tool_name": "query_device_terminals_typo",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true
  }
 }</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>{"unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>工具无效，拒绝触发</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -4245,12 +4513,12 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>工具错配</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4535,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -4278,23 +4546,24 @@
       <c r="E65" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs_typo",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminals_typo",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ]
  }
 }</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"]}</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -4309,7 +4578,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>contains: 无进出记录 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
@@ -4331,7 +4600,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>指令注入日志查询</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -4342,22 +4611,22 @@
       <c r="E66" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>指令注入日志查询</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>{"date_to": "今日", "event_type": ""}</t>
+          <t>{"page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -4372,7 +4641,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>contains: 参数非法 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
@@ -4394,37 +4663,40 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_remaining_visitors",
- "tool_params": {
-  "unknown_param": "x"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "operationSources": "",
+  "page": -1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>{"unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": -1, "size": 10}</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -4434,12 +4706,12 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>contains: 未离场人员清单 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -4456,37 +4728,45 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_unattended_status",
- "tool_params": {
-  "unknown_param": "x"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": 0,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>{"unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "portIds": ["26456101370181"], "page": 0, "size": 10}</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -4496,12 +4776,12 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>contains: 当前值守模式状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -4518,31 +4798,41 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>错误处理</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "disable_unattended_mode_typo",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "startTime": "",
+  "endTime": "",
+  "page": "abc",
+  "size": 10
+ }
 }</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
+          <t>按时间范围查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "startTime": "", "endTime": "", "page": "abc", "size": 10}</t>
+        </is>
+      </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>参数类型错误被拒绝/提示</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -4552,12 +4842,12 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>contains: 关闭结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>类型错配</t>
         </is>
       </c>
     </row>
@@ -4574,37 +4864,41 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_door_lock_status",
- "tool_params": {
-  "unknown_param": "x"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "startTime": "",
+  "endTime": "",
+  "page": 9999999999999999,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>{"unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "startTime": "", "endTime": "", "page": 9999999999999999, "size": 10}</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4614,12 +4908,12 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>contains: 门锁设备状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -4636,31 +4930,38 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>输入输出契约</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_remaining_visitors_typo",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "unknown_param": "x"
+ }
 }</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
+          <t>查询设备终端列表</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "unknown_param": "x"}</t>
+        </is>
+      </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>未知参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4670,12 +4971,12 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>contains: 未离场人员清单 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>参数注入</t>
         </is>
       </c>
     </row>
@@ -4692,31 +4993,38 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "unlock_door_typo",
- "tool_params": {}
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": 0
+ }
 }</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr"/>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": 0}</t>
+        </is>
+      </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4726,12 +5034,12 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -4748,31 +5056,40 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>错误处理</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "operationSources": "",
+  "page": "abc",
+  "size": 10
+ }
 }</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
+          <t>按操作来源筛选端口记录</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": "abc", "size": 10}</t>
+        </is>
+      </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>缺失参数被拒绝/提示</t>
+          <t>参数类型错误被拒绝/提示</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4782,12 +5099,12 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>参数缺失</t>
+          <t>类型错配</t>
         </is>
       </c>
     </row>
@@ -4804,37 +5121,38 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>未确认开启</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "unknown_param": "x"
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": -1
  }
 }</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>未确认开启</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>{"unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "isEnabled": -1}</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -4844,12 +5162,12 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -4866,37 +5184,39 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>触发条件正确性</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "unlock_door",
- "tool_params": {
-  "unknown_param": "x"
+ "tool_name": "query_device_terminal_port_state_records_typo",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>{"unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>工具无效，拒绝触发</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4906,12 +5226,12 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>工具错配</t>
         </is>
       </c>
     </row>
@@ -4928,7 +5248,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>指令注入日志查询</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -4939,11 +5259,12 @@
       <c r="E76" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": "",
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ],
   "unknown_param": "x"
  }
 }</t>
@@ -4951,12 +5272,12 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>指令注入日志查询</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": "", "unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "unknown_param": "x"}</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -4971,7 +5292,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>contains: 参数非法 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
@@ -4993,31 +5314,40 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>未确认开启</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>输入输出契约</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode_typo",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 1,
+  "size": 10,
+  "unknown_param": "x"
+ }
 }</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>未确认开启</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr"/>
+          <t>查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10, "unknown_param": "x"}</t>
+        </is>
+      </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>未知参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -5027,12 +5357,12 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>参数注入</t>
         </is>
       </c>
     </row>
@@ -5049,40 +5379,38 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": "",
-  "unknown_param": "x"
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": 9999999999999999
  }
 }</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": "", "unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "isEnabled": 9999999999999999}</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -5092,12 +5420,12 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5442,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>指令注入日志查询</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -5125,23 +5453,29 @@
       <c r="E79" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs_typo",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records_typo",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>指令注入日志查询</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "portIds": ["26456101370181"], "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -5156,7 +5490,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>contains: 参数非法 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
@@ -5178,38 +5512,41 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>触发条件正确性</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records_typo",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "startTime": "",
+  "endTime": "",
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>{"date_to": "今日", "event_type": ""}</t>
+          <t>{"merchantId": "26377732552517", "startTime": "", "endTime": "", "page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>缺失参数被拒绝/提示</t>
+          <t>工具无效，拒绝触发</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -5219,12 +5556,12 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>contains: 无进出记录 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>参数缺失</t>
+          <t>工具错配</t>
         </is>
       </c>
     </row>
@@ -5241,37 +5578,42 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>输入输出契约</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs_typo",
- "tool_params": {
-  "storeId": "XHM-BATCH-002"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "startTime": "",
+  "endTime": "",
+  "page": 1,
+  "size": 10,
+  "unknown_param": "x"
  }
 }</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>{"storeId": "XHM-BATCH-002"}</t>
+          <t>{"merchantId": "26377732552517", "startTime": "", "endTime": "", "page": 1, "size": 10, "unknown_param": "x"}</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>未知参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -5281,12 +5623,12 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>参数注入</t>
         </is>
       </c>
     </row>
@@ -5303,31 +5645,37 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>输入输出契约</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_unattended_status_typo",
- "tool_params": {}
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "isEnabled": true
+ }
 }</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr"/>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>{"isEnabled": true}</t>
+        </is>
+      </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>缺失参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -5337,12 +5685,12 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>contains: 当前值守模式状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>参数缺失</t>
         </is>
       </c>
     </row>
@@ -5359,37 +5707,39 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "disable_unattended_mode",
- "tool_params": {
-  "unknown_param": "x"
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": -1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>{"unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "page": -1, "size": 10}</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -5399,12 +5749,12 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>contains: 关闭结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -5421,37 +5771,38 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>开启无人值守模式</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode",
- "tool_params": {
-  "unknown_param": "x"
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": 9999999999999999
  }
 }</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>开启无人值守模式</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>{"unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "isEnabled": 9999999999999999}</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -5461,12 +5812,12 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>contains: 开启结果 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -5483,31 +5834,39 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "get_door_lock_status_typo",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 0,
+  "size": 10
+ }
 }</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr"/>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 0, "size": 10}</t>
+        </is>
+      </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -5517,12 +5876,12 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>contains: 门锁设备状态 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -5539,40 +5898,38 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_from": "今日",
-  "date_to": "今日",
-  "event_type": "",
-  "unknown_param": "x"
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": 0
  }
 }</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>{"date_from": "今日", "date_to": "今日", "event_type": "", "unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517", "isEnabled": 0}</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -5582,12 +5939,12 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>contains: 无进出记录 | 错误 | 拒绝  any_of=true</t>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -5604,31 +5961,39 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>触发条件正确性</t>
+          <t>能力边界</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "enable_unattended_mode_typo",
- "tool_params": {}
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 9999999999999999,
+  "size": 10
+ }
 }</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>设备离线开启</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr"/>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 9999999999999999, "size": 10}</t>
+        </is>
+      </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>工具无效，拒绝触发</t>
+          <t>越界参数被拒绝/提示</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -5638,12 +6003,12 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>工具错配</t>
+          <t>数值变异</t>
         </is>
       </c>
     </row>
@@ -5660,38 +6025,37 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>输入输出契约</t>
+          <t>触发条件正确性</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "storeId": "XHM-BATCH-002",
-  "unknown_param": "x"
+ "tool_name": "query_device_terminals_typo",
+ "tool_params": {
+  "merchantId": "26377732552517"
  }
 }</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>越权查询日志</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>{"storeId": "XHM-BATCH-002", "unknown_param": "x"}</t>
+          <t>{"merchantId": "26377732552517"}</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>未知参数被拒绝/提示</t>
+          <t>工具无效，拒绝触发</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -5701,12 +6065,12 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>参数注入</t>
+          <t>工具错配</t>
         </is>
       </c>
     </row>
@@ -5723,7 +6087,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -5734,22 +6098,22 @@
       <c r="E89" s="3" t="inlineStr">
         <is>
           <t>{
- "tool_name": "query_access_logs",
- "tool_params": {
-  "date_to": "今日",
-  "event_type": ""
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "page": 1,
+  "size": 10
  }
 }</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>{"date_to": "今日", "event_type": ""}</t>
+          <t>{"page": 1, "size": 10}</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -5764,7 +6128,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>contains: 错误 | 拒绝  any_of=true</t>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
@@ -5786,51 +6150,898 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
+          <t>能力边界</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": -1
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": -1}</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-090</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>错误处理</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": "abc",
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": "abc", "size": 10}</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>参数类型错误被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>类型错配</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-091</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>能力边界</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 9999999999999999,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 9999999999999999, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>contains: Test | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-092</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>输入输出契约</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true,
+  "unknown_param": "x"
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true, "unknown_param": "x"}</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>未知参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>参数注入</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-093</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>错误处理</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminals",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": "abc"
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>先查终端再开启无人值守</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": "abc"}</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>参数类型错误被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>类型错配</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-094</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>按操作来源筛选端口记录</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>能力边界</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "operationSources": "",
+  "page": 0,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>按操作来源筛选端口记录</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": 0, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-095</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>开启无人值守模式</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>能力边界</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "set_device_terminal_unattended_mode",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": 0
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>开启无人值守模式</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": 0}</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-096</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
           <t>触发条件正确性</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>{
- "tool_name": "enable_unattended_mode_typo",
- "tool_params": {}
-}</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>开启无人值守</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr"/>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "set_device_terminal_unattended_mode_typo",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "isEnabled": true
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>关闭无人值守模式</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "isEnabled": true}</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
         <is>
           <t>工具无效，拒绝触发</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>contains: 开启结果 | 错误 | 拒绝  any_of=true</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>contains: isEnable | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
         <is>
           <t>工具错配</t>
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-097</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>按终端/端口筛选端口记录</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>错误处理</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "terminalIds": [
+   "26456010686725"
+  ],
+  "portIds": [
+   "26456101370181"
+  ],
+  "page": "abc",
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>按终端/端口筛选端口记录</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "terminalIds": ["26456010686725"], "portIds": ["26456101370181"], "page": "abc", "size": 10}</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>参数类型错误被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>类型错配</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-098</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>按操作来源筛选端口记录</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>触发条件正确性</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records_typo",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "operationSources": "",
+  "page": 1,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>按操作来源筛选端口记录</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": 1, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>工具无效，拒绝触发</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>工具错配</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-099</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>触发条件正确性</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records_typo",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 1,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>工具无效，拒绝触发</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>工具错配</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>输入输出契约</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "page": 1,
+  "size": 10,
+  "unknown_param": "x"
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>组合查询端口记录与终端状态</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "page": 1, "size": 10, "unknown_param": "x"}</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>未知参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>contains: 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>参数注入</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-101</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>按时间范围查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>输入输出契约</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "startTime": "",
+  "endTime": "",
+  "page": 1,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>按时间范围查询端口操作记录</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>{"startTime": "", "endTime": "", "page": 1, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>缺失参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>contains: 端口操作记录 | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>参数缺失</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>D-L2-102</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>按操作来源筛选端口记录</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>能力边界</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>{
+ "tool_name": "query_device_terminal_port_state_records",
+ "tool_params": {
+  "merchantId": "26377732552517",
+  "operationSources": "",
+  "page": 9999999999999999,
+  "size": 10
+ }
+}</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>按操作来源筛选端口记录</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>{"merchantId": "26377732552517", "operationSources": "", "page": 9999999999999999, "size": 10}</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>越界参数被拒绝/提示</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>contains: 记录 | 拒绝 | 错误  any_of=true</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>数值变异</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K90"/>
+  <autoFilter ref="A1:K103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5841,7 +7052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5899,20 +7110,20 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>关闭无人值守</t>
+          <t>先查终端再开启无人值守</t>
         </is>
       </c>
       <c r="B2" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>1</v>
@@ -5921,13 +7132,13 @@
         <v>0</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>开启无人值守</t>
+          <t>关闭无人值守模式</t>
         </is>
       </c>
       <c r="B3" s="8" t="n">
@@ -5937,10 +7148,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="8" t="n">
         <v>1</v>
@@ -5949,23 +7160,23 @@
         <v>0</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>强制解锁门锁</t>
+          <t>开启无人值守模式</t>
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>1</v>
@@ -5977,26 +7188,26 @@
         <v>0</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>指令注入日志查询</t>
+          <t>按操作来源筛选端口记录</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>1</v>
@@ -6005,13 +7216,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>无数据日志查询</t>
+          <t>按时间范围查询端口操作记录</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -6021,10 +7232,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>1</v>
@@ -6033,13 +7244,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>未确认开启</t>
+          <t>按终端/端口筛选端口记录</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -6049,10 +7260,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>1</v>
@@ -6061,26 +7272,26 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>查询值守状态</t>
+          <t>查询端口操作记录</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1</v>
@@ -6089,20 +7300,20 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>查询未离场人员</t>
+          <t>查询设备终端列表</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>1</v>
@@ -6113,24 +7324,24 @@
       <c r="F9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>0</v>
+      <c r="G9" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>查询门禁日志</t>
+          <t>查询设备终端详情</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>1</v>
@@ -6145,91 +7356,35 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>查询门锁状态</t>
+          <t>组合查询端口记录与终端状态</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="8" t="n">
-        <v>1</v>
+      <c r="G11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>设备离线开启</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>越权查询日志</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -6275,7 +7430,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -6290,7 +7445,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTIF(用例明细!$B$2:$B$90,"L1")</f>
+        <f>COUNTIF(用例明细!$B$2:$B$103,"L1")</f>
         <v/>
       </c>
       <c r="C3" s="7">
@@ -6305,7 +7460,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTIF(用例明细!$B$2:$B$90,"L2")</f>
+        <f>COUNTIF(用例明细!$B$2:$B$103,"L2")</f>
         <v/>
       </c>
       <c r="C4" s="7">
@@ -6320,7 +7475,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(用例明细!$B$2:$B$90,"L3")</f>
+        <f>COUNTIF(用例明细!$B$2:$B$103,"L3")</f>
         <v/>
       </c>
       <c r="C5" s="7">
@@ -6335,7 +7490,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF(用例明细!$I$2:$I$90,"是")</f>
+        <f>COUNTIF(用例明细!$I$2:$I$103,"是")</f>
         <v/>
       </c>
       <c r="C6" s="7" t="inlineStr">
